--- a/na_avtomat(2).xlsx
+++ b/na_avtomat(2).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tasdm\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danila\Documents\Repoes\opt\Optimization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D99B01D-6ECD-4F5A-B8DB-A1A4E8CA6B57}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DF1DE2-DFB9-4920-826C-07AD6DE62342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3945" yWindow="3015" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="465" yWindow="990" windowWidth="17655" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="пример 1" sheetId="2" r:id="rId1"/>
@@ -1053,7 +1053,7 @@
         <v>68</v>
       </c>
       <c r="E26" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1070,7 +1070,7 @@
         <v>68</v>
       </c>
       <c r="E27" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
